--- a/Result/profitability/8038.xlsx
+++ b/Result/profitability/8038.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002499999999999988</v>
+        <v>0.01125</v>
       </c>
       <c r="N2" t="n">
-        <v>31.0075</v>
+        <v>29.91875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02124999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="N3" t="n">
-        <v>28.52375</v>
+        <v>29.11625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.02625000000000001</v>
+        <v>-0.03000000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>32.45625</v>
+        <v>26.63875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06875000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="N5" t="n">
-        <v>30.79125</v>
+        <v>28.98</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09875</v>
+        <v>-0.21125</v>
       </c>
       <c r="N6" t="n">
-        <v>33.93375</v>
+        <v>31.62</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.17875</v>
+        <v>-0.21875</v>
       </c>
       <c r="N7" t="n">
-        <v>35.50625</v>
+        <v>35.0175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-1.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.335</v>
+        <v>-0.39125</v>
       </c>
       <c r="N8" t="n">
-        <v>37.93125</v>
+        <v>35.47125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9068,6 +9068,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>180</v>
+      </c>
+      <c r="D69" t="n">
+        <v>154</v>
+      </c>
+      <c r="E69" t="n">
+        <v>26</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-5.98%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.04874999999999999</v>
+      </c>
+      <c r="N69" t="n">
+        <v>27.5975</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-1.875</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-19.68</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.5807022720566539</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.5048780487804878</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
